--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-fev-fvc.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-fev-fvc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1747,6 +1747,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1865,6 +1872,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12011,7 +12022,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -12069,7 +12080,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12080,10 +12091,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12195,10 +12206,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12312,10 +12323,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12431,10 +12442,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12460,13 +12471,13 @@
         <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>261</v>
@@ -12518,7 +12529,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>91</v>
@@ -12536,7 +12547,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>266</v>
@@ -12550,10 +12561,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12576,16 +12587,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>386</v>
@@ -12637,7 +12648,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12655,7 +12666,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>389</v>
@@ -12669,10 +12680,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12698,13 +12709,13 @@
         <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>434</v>
@@ -12756,7 +12767,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12788,10 +12799,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12817,10 +12828,10 @@
         <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>443</v>
@@ -12875,7 +12886,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12907,10 +12918,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12936,10 +12947,10 @@
         <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>494</v>
@@ -12994,7 +13005,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13026,13 +13037,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
@@ -13057,10 +13068,10 @@
         <v>491</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>552</v>
@@ -13136,7 +13147,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13147,10 +13158,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13262,10 +13273,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13379,10 +13390,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13498,10 +13509,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13527,13 +13538,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>261</v>
@@ -13585,7 +13596,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13603,7 +13614,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>266</v>
@@ -13617,10 +13628,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13732,10 +13743,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13849,10 +13860,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13924,7 +13935,7 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -13966,10 +13977,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>274</v>
@@ -14085,10 +14096,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>321</v>
@@ -14204,10 +14215,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14323,10 +14334,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14349,16 +14360,16 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>386</v>
@@ -14398,7 +14409,7 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
@@ -14408,7 +14419,7 @@
         <v>117</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14426,7 +14437,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>389</v>
@@ -14440,13 +14451,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>81</v>
@@ -14471,13 +14482,13 @@
         <v>382</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>386</v>
@@ -14529,7 +14540,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14547,7 +14558,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>389</v>
@@ -14561,10 +14572,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14676,10 +14687,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14793,10 +14804,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14912,10 +14923,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15031,10 +15042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15148,10 +15159,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15265,10 +15276,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15384,10 +15395,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15413,13 +15424,13 @@
         <v>232</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>434</v>
@@ -15471,7 +15482,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15503,10 +15514,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15532,10 +15543,10 @@
         <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>443</v>
@@ -15590,7 +15601,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15622,10 +15633,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15651,10 +15662,10 @@
         <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>494</v>
@@ -15709,7 +15720,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15741,13 +15752,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
@@ -15772,10 +15783,10 @@
         <v>491</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>552</v>
@@ -15851,7 +15862,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15862,10 +15873,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15977,10 +15988,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16094,10 +16105,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16213,10 +16224,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16242,13 +16253,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>261</v>
@@ -16300,7 +16311,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>91</v>
@@ -16318,7 +16329,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>266</v>
@@ -16332,10 +16343,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16447,10 +16458,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16564,10 +16575,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16639,7 +16650,7 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16681,10 +16692,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>274</v>
@@ -16800,10 +16811,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>321</v>
@@ -16919,10 +16930,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17038,10 +17049,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17064,16 +17075,16 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>386</v>
@@ -17113,7 +17124,7 @@
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17123,7 +17134,7 @@
         <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17141,7 +17152,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>389</v>
@@ -17155,13 +17166,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
@@ -17186,13 +17197,13 @@
         <v>382</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>386</v>
@@ -17244,7 +17255,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17262,7 +17273,7 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>389</v>
@@ -17276,10 +17287,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17391,10 +17402,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17508,10 +17519,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17627,10 +17638,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17746,10 +17757,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17863,10 +17874,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17980,10 +17991,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18099,10 +18110,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18128,13 +18139,13 @@
         <v>232</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>434</v>
@@ -18186,7 +18197,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18218,10 +18229,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18247,10 +18258,10 @@
         <v>232</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>443</v>
@@ -18305,7 +18316,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18337,10 +18348,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18366,10 +18377,10 @@
         <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>494</v>
@@ -18424,7 +18435,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18456,13 +18467,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
@@ -18487,10 +18498,10 @@
         <v>491</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>552</v>
@@ -18566,7 +18577,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18577,10 +18588,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18692,10 +18703,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18809,10 +18820,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18928,10 +18939,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18957,13 +18968,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>261</v>
@@ -19015,7 +19026,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -19033,7 +19044,7 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>266</v>
@@ -19047,10 +19058,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19162,10 +19173,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19279,10 +19290,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19354,7 +19365,7 @@
         <v>81</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19396,10 +19407,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>274</v>
@@ -19446,7 +19457,7 @@
         <v>81</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>81</v>
@@ -19465,7 +19476,7 @@
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
@@ -19515,10 +19526,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19634,10 +19645,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19660,16 +19671,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>386</v>
@@ -19721,7 +19732,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19739,7 +19750,7 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>389</v>
@@ -19753,10 +19764,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19782,13 +19793,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>434</v>
@@ -19840,7 +19851,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19872,10 +19883,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19901,10 +19912,10 @@
         <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>443</v>
@@ -19959,7 +19970,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19991,10 +20002,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20020,10 +20031,10 @@
         <v>82</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>494</v>
@@ -20078,7 +20089,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
